--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BFA8557-D6C8-4BD9-80F1-960BE94C8313}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordenador" sheetId="1" r:id="rId1"/>
@@ -89,9 +89,6 @@
     <t>RAFAEL V. - CDAP L</t>
   </si>
   <si>
-    <t>patricia.reggo@hotmail.com</t>
-  </si>
-  <si>
     <t>PATRICIA P. - CDC SP Int</t>
   </si>
   <si>
@@ -228,6 +225,9 @@
   </si>
   <si>
     <t>Coordenador</t>
+  </si>
+  <si>
+    <t>perrone@adere.com</t>
   </si>
 </sst>
 </file>
@@ -633,87 +633,87 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -721,111 +721,111 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -833,31 +833,31 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">

--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BFA8557-D6C8-4BD9-80F1-960BE94C8313}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A7EC1C-A204-4D27-995F-105FEC82E4CF}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>JEFFERSON N. - CIC Leste</t>
   </si>
   <si>
-    <t>ivanes.santos@adere.com</t>
-  </si>
-  <si>
     <t>IVANES S. - CDC Sul</t>
   </si>
   <si>
@@ -228,6 +225,9 @@
   </si>
   <si>
     <t>perrone@adere.com</t>
+  </si>
+  <si>
+    <t>alefef4@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -633,87 +633,87 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -721,82 +721,82 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">

--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A7EC1C-A204-4D27-995F-105FEC82E4CF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9752D044-5580-4F63-A029-C769E494DB5A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
@@ -224,10 +224,10 @@
     <t>Coordenador</t>
   </si>
   <si>
-    <t>perrone@adere.com</t>
-  </si>
-  <si>
     <t>alefef4@gmail.com</t>
+  </si>
+  <si>
+    <t>ivanes.santos@adere.com</t>
   </si>
 </sst>
 </file>

--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9752D044-5580-4F63-A029-C769E494DB5A}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E7C1C2-F2F3-4EA3-9DFF-C5A7567152EB}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
@@ -224,10 +224,10 @@
     <t>Coordenador</t>
   </si>
   <si>
-    <t>alefef4@gmail.com</t>
-  </si>
-  <si>
     <t>ivanes.santos@adere.com</t>
+  </si>
+  <si>
+    <t>perrone@adere.com</t>
   </si>
 </sst>
 </file>
@@ -796,7 +796,7 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">

--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E7C1C2-F2F3-4EA3-9DFF-C5A7567152EB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E708D03D-9DF3-476B-8DAB-D2111B41095B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordenador" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>NORDESTE</t>
   </si>
   <si>
-    <t>misael@adere.com</t>
-  </si>
-  <si>
     <t>MISAEL A. - GRU TRANSP</t>
   </si>
   <si>
@@ -228,6 +225,9 @@
   </si>
   <si>
     <t>perrone@adere.com</t>
+  </si>
+  <si>
+    <t>hellenbianchini19@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -296,9 +296,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7D0D8BA-1C25-4BDF-BAA6-CC2DDC94289D}" name="TabelaCoordenadoremail" displayName="TabelaCoordenadoremail" ref="A1:B42" totalsRowShown="0">
   <autoFilter ref="A1:B42" xr:uid="{2879466B-4584-4DB2-8267-9C0550F222C2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B42">
-    <sortCondition ref="A8:A42"/>
-  </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{38FA9509-12B5-44C7-B74C-22E0AC056129}" name="Coordenador"/>
     <tableColumn id="2" xr3:uid="{D67CC50D-6F7A-46EA-8C4A-DAB37A42691F}" name="E-mail"/>
@@ -633,87 +630,87 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -721,111 +718,111 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -833,26 +830,26 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,7 +873,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">

--- a/E-mailsCoordenador.xlsx
+++ b/E-mailsCoordenador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E708D03D-9DF3-476B-8DAB-D2111B41095B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{96A63D2C-51B8-4BFD-BBD0-4A4AA1A9D257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6074C7D-9361-4512-AE2B-B6B35318105E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C6FA2A1-41B6-4DE6-858A-3C0DB5BAEDC7}"/>
   </bookViews>
@@ -227,7 +227,7 @@
     <t>perrone@adere.com</t>
   </si>
   <si>
-    <t>hellenbianchini19@gmail.com</t>
+    <t>misael@adere.com</t>
   </si>
 </sst>
 </file>
